--- a/diseases/d026/2026-2029.xlsx
+++ b/diseases/d026/2026-2029.xlsx
@@ -27712,6 +27712,402 @@
         </is>
       </c>
     </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>D026</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>typhoid-and-paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Typhoid and Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>D026</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Typhoid and Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>伤寒和副伤寒</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N148" t="n">
+        <v>454</v>
+      </c>
+      <c r="O148" t="n">
+        <v>454</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>0</v>
+      </c>
+      <c r="R148" t="n">
+        <v>0.03213217305250191</v>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO148" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP148" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ148" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS148" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT148" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU148" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV148" t="inlineStr">
+        <is>
+          <t>cdc_weekly</t>
+        </is>
+      </c>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>China CDC Weekly</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>cdc_weekly; nhc; pubmed</t>
+        </is>
+      </c>
+      <c r="BA148" t="inlineStr">
+        <is>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+        </is>
+      </c>
+      <c r="BB148" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+        </is>
+      </c>
+      <c r="BC148" t="inlineStr">
+        <is>
+          <t>web; web; web</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>D026</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>typhoid-and-paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Typhoid and Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>D026</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Typhoid and Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>伤寒和副伤寒</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N149" t="n">
+        <v>454</v>
+      </c>
+      <c r="O149" t="n">
+        <v>454</v>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>SRC_CN_CDC</t>
+        </is>
+      </c>
+      <c r="X149" t="inlineStr">
+        <is>
+          <t>伤寒和副伤寒</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>country:CN:national</t>
+        </is>
+      </c>
+      <c r="AD149" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE149" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF149" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG149" t="inlineStr">
+        <is>
+          <t>reported_aggregate</t>
+        </is>
+      </c>
+      <c r="AH149" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI149" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ149" t="inlineStr">
+        <is>
+          <t>CN_CDC_current</t>
+        </is>
+      </c>
+      <c r="AK149" t="inlineStr">
+        <is>
+          <t>China CDC source-reported combined typhoid-and-paratyphoid notifications.</t>
+        </is>
+      </c>
+      <c r="AM149" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN149" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO149" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP149" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ149" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS149" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT149" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU149" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV149" t="inlineStr">
+        <is>
+          <t>cdc_weekly</t>
+        </is>
+      </c>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>China CDC Weekly</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>cdc_weekly; nhc; pubmed</t>
+        </is>
+      </c>
+      <c r="BA149" t="inlineStr">
+        <is>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+        </is>
+      </c>
+      <c r="BB149" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+        </is>
+      </c>
+      <c r="BC149" t="inlineStr">
+        <is>
+          <t>web; web; web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -27745,7 +28141,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -27828,7 +28224,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10">
@@ -27838,7 +28234,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11">
@@ -27858,7 +28254,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -27890,7 +28286,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3191</v>
+        <v>3645</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d026/2026-2029.xlsx
+++ b/diseases/d026/2026-2029.xlsx
@@ -24850,12 +24850,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>CN-GD</t>
+          <t>CN-FJ</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Guangdong, China</t>
+          <t>Fujian, China</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -24889,10 +24889,10 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="O132" t="n">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -24964,7 +24964,7 @@
       </c>
       <c r="BB132" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.fujian.gov.cn/xxgk/zfxxgkzl/zfxxgkml/ggws/fdcrbyqgb/</t>
         </is>
       </c>
       <c r="BC132" t="inlineStr">
@@ -25001,12 +25001,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>CN-GD</t>
+          <t>CN-FJ</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Guangdong, China</t>
+          <t>Fujian, China</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -25040,10 +25040,10 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="O133" t="n">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="U133" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>country:CN-GD:national</t>
+          <t>country:CN-FJ:national</t>
         </is>
       </c>
       <c r="AD133" t="inlineStr">
@@ -25198,7 +25198,7 @@
       </c>
       <c r="BB133" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.fujian.gov.cn/xxgk/zfxxgkzl/zfxxgkml/ggws/fdcrbyqgb/</t>
         </is>
       </c>
       <c r="BC133" t="inlineStr">
@@ -25235,12 +25235,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>CN-HN</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hunan, China</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -25274,10 +25274,10 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="O134" t="n">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
@@ -25349,7 +25349,7 @@
       </c>
       <c r="BB134" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC134" t="inlineStr">
@@ -25386,12 +25386,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>CN-HN</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hunan, China</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -25425,10 +25425,10 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="O135" t="n">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="U135" t="inlineStr">
         <is>
@@ -25472,7 +25472,7 @@
       </c>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>country:CN-HN:national</t>
+          <t>country:CN-GD:national</t>
         </is>
       </c>
       <c r="AD135" t="inlineStr">
@@ -25583,7 +25583,7 @@
       </c>
       <c r="BB135" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC135" t="inlineStr">
@@ -25620,12 +25620,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -25659,10 +25659,10 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="O136" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
@@ -25734,7 +25734,7 @@
       </c>
       <c r="BB136" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC136" t="inlineStr">
@@ -25771,12 +25771,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -25810,10 +25810,10 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="O137" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="U137" t="inlineStr">
         <is>
@@ -25857,7 +25857,7 @@
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>country:CN-JS:national</t>
+          <t>country:CN-HN:national</t>
         </is>
       </c>
       <c r="AD137" t="inlineStr">
@@ -25968,7 +25968,7 @@
       </c>
       <c r="BB137" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC137" t="inlineStr">
@@ -26005,12 +26005,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>CN-LN</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Liaoning, China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -26044,10 +26044,10 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O138" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
@@ -26119,7 +26119,7 @@
       </c>
       <c r="BB138" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC138" t="inlineStr">
@@ -26156,12 +26156,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>CN-LN</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Liaoning, China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -26195,10 +26195,10 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O139" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="U139" t="inlineStr">
         <is>
@@ -26242,7 +26242,7 @@
       </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>country:CN-LN:national</t>
+          <t>country:CN-JS:national</t>
         </is>
       </c>
       <c r="AD139" t="inlineStr">
@@ -26353,7 +26353,7 @@
       </c>
       <c r="BB139" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC139" t="inlineStr">
@@ -26390,12 +26390,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>CN-SC</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Sichuan, China</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -26429,10 +26429,10 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="O140" t="n">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
@@ -26504,7 +26504,7 @@
       </c>
       <c r="BB140" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC140" t="inlineStr">
@@ -26541,12 +26541,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>CN-SC</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Sichuan, China</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -26580,10 +26580,10 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="O141" t="n">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="U141" t="inlineStr">
         <is>
@@ -26627,7 +26627,7 @@
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>country:CN-SC:national</t>
+          <t>country:CN-LN:national</t>
         </is>
       </c>
       <c r="AD141" t="inlineStr">
@@ -26738,7 +26738,7 @@
       </c>
       <c r="BB141" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC141" t="inlineStr">
@@ -26775,12 +26775,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -26814,10 +26814,10 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="O142" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
@@ -26889,7 +26889,7 @@
       </c>
       <c r="BB142" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC142" t="inlineStr">
@@ -26926,12 +26926,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -26965,10 +26965,10 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="O143" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="U143" t="inlineStr">
         <is>
@@ -27012,7 +27012,7 @@
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>country:CN-SH:national</t>
+          <t>country:CN-SC:national</t>
         </is>
       </c>
       <c r="AD143" t="inlineStr">
@@ -27123,7 +27123,7 @@
       </c>
       <c r="BB143" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC143" t="inlineStr">
@@ -27160,12 +27160,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -27190,7 +27190,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -27204,76 +27204,82 @@
       <c r="O144" t="n">
         <v>0</v>
       </c>
-      <c r="R144" t="n">
-        <v>0</v>
-      </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO144" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR144" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS144" t="inlineStr"/>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ144" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS144" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_TYPHOID_PARATYPHOID; SER_CN_PROV_REPORT_TYPHOID_PARATYPHOID</t>
+        </is>
+      </c>
       <c r="AT144" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU144" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV144" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA144" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB144" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC144" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -27300,17 +27306,17 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -27335,7 +27341,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -27349,76 +27355,165 @@
       <c r="O145" t="n">
         <v>0</v>
       </c>
-      <c r="R145" t="n">
-        <v>0</v>
-      </c>
-      <c r="S145" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_TYPHOID_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_TYPHOID_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X145" t="inlineStr">
+        <is>
+          <t>伤寒和副伤寒</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>country:CN-SH:national</t>
+        </is>
+      </c>
+      <c r="AD145" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE145" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF145" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG145" t="inlineStr">
+        <is>
+          <t>reported_aggregate</t>
+        </is>
+      </c>
+      <c r="AH145" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI145" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ145" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK145" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM145" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN145" t="b">
+        <v>1</v>
       </c>
       <c r="AO145" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR145" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS145" t="inlineStr"/>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ145" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS145" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_TYPHOID_PARATYPHOID; SER_CN_PROV_REPORT_TYPHOID_PARATYPHOID</t>
+        </is>
+      </c>
       <c r="AT145" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA145" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB145" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC145" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -27480,7 +27575,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -27489,13 +27584,13 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O146" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R146" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0</v>
       </c>
       <c r="S146" t="inlineStr">
         <is>
@@ -27625,7 +27720,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -27740,12 +27835,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -27770,107 +27865,90 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N148" t="n">
-        <v>454</v>
+        <v>2</v>
       </c>
       <c r="O148" t="n">
-        <v>454</v>
-      </c>
-      <c r="Q148" t="n">
+        <v>2</v>
+      </c>
+      <c r="R148" t="n">
+        <v>0.0005730076265538771</v>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO148" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP148" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR148" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS148" t="inlineStr"/>
+      <c r="AT148" t="n">
         <v>0</v>
       </c>
-      <c r="R148" t="n">
-        <v>0.03213217305250191</v>
-      </c>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U148" t="inlineStr">
-        <is>
-          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA148" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO148" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="AP148" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ148" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS148" t="inlineStr">
-        <is>
-          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT148" t="n">
-        <v>1</v>
-      </c>
       <c r="AU148" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV148" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA148" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB148" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC148" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -27897,214 +27975,3216 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>D026</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Typhoid and Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>伤寒和副伤寒</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N149" t="n">
+        <v>0</v>
+      </c>
+      <c r="O149" t="n">
+        <v>0</v>
+      </c>
+      <c r="R149" t="n">
+        <v>0</v>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO149" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP149" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR149" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS149" t="inlineStr"/>
+      <c r="AT149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU149" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV149" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA149" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB149" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC149" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>D026</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>typhoid-and-paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Typhoid and Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>D026</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Typhoid and Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>伤寒和副伤寒</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N150" t="n">
+        <v>454</v>
+      </c>
+      <c r="O150" t="n">
+        <v>454</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>0</v>
+      </c>
+      <c r="R150" t="n">
+        <v>0.03213217305250191</v>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO150" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP150" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ150" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS150" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT150" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU150" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV150" t="inlineStr">
+        <is>
+          <t>cdc_weekly</t>
+        </is>
+      </c>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>China CDC Weekly</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>cdc_weekly; nhc; pubmed</t>
+        </is>
+      </c>
+      <c r="BA150" t="inlineStr">
+        <is>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+        </is>
+      </c>
+      <c r="BB150" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+        </is>
+      </c>
+      <c r="BC150" t="inlineStr">
+        <is>
+          <t>web; web; web</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>D026</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>typhoid-and-paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Typhoid and Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
           <t>source_series_observation</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr">
+      <c r="F151" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr">
+      <c r="G151" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>D026</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>Typhoid and Paratyphoid fever</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>D026</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Typhoid and Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
         <is>
           <t>伤寒和副伤寒</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr">
+      <c r="K151" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L149" t="inlineStr">
+      <c r="L151" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="M149" t="inlineStr">
+      <c r="M151" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="N149" t="n">
+      <c r="N151" t="n">
         <v>454</v>
       </c>
-      <c r="O149" t="n">
+      <c r="O151" t="n">
         <v>454</v>
       </c>
-      <c r="U149" t="inlineStr">
+      <c r="U151" t="inlineStr">
         <is>
           <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
         </is>
       </c>
-      <c r="V149" t="inlineStr">
+      <c r="V151" t="inlineStr">
         <is>
           <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
         </is>
       </c>
-      <c r="W149" t="inlineStr">
+      <c r="W151" t="inlineStr">
         <is>
           <t>SRC_CN_CDC</t>
         </is>
       </c>
-      <c r="X149" t="inlineStr">
+      <c r="X151" t="inlineStr">
         <is>
           <t>伤寒和副伤寒</t>
         </is>
       </c>
-      <c r="Y149" t="inlineStr">
+      <c r="Y151" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z149" t="inlineStr">
+      <c r="Z151" t="inlineStr">
         <is>
           <t>notification</t>
         </is>
       </c>
-      <c r="AA149" t="inlineStr">
+      <c r="AA151" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB149" t="inlineStr">
+      <c r="AB151" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC149" t="inlineStr">
+      <c r="AC151" t="inlineStr">
         <is>
           <t>country:CN:national</t>
         </is>
       </c>
-      <c r="AD149" t="inlineStr">
+      <c r="AD151" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE149" t="inlineStr">
+      <c r="AE151" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF149" t="inlineStr">
+      <c r="AF151" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="AG149" t="inlineStr">
+      <c r="AG151" t="inlineStr">
         <is>
           <t>reported_aggregate</t>
         </is>
       </c>
-      <c r="AH149" t="inlineStr">
+      <c r="AH151" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI149" t="inlineStr">
+      <c r="AI151" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ149" t="inlineStr">
+      <c r="AJ151" t="inlineStr">
         <is>
           <t>CN_CDC_current</t>
         </is>
       </c>
-      <c r="AK149" t="inlineStr">
+      <c r="AK151" t="inlineStr">
         <is>
           <t>China CDC source-reported combined typhoid-and-paratyphoid notifications.</t>
         </is>
       </c>
-      <c r="AM149" t="inlineStr">
+      <c r="AM151" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="AN149" t="b">
+      <c r="AN151" t="b">
         <v>1</v>
       </c>
-      <c r="AO149" t="inlineStr">
+      <c r="AO151" t="inlineStr">
         <is>
           <t>mixed</t>
         </is>
       </c>
-      <c r="AP149" t="inlineStr">
+      <c r="AP151" t="inlineStr">
         <is>
           <t>single_series</t>
         </is>
       </c>
-      <c r="AQ149" t="inlineStr">
+      <c r="AQ151" t="inlineStr">
         <is>
           <t>legacy_gap_fill</t>
         </is>
       </c>
-      <c r="AS149" t="inlineStr">
+      <c r="AS151" t="inlineStr">
         <is>
           <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
         </is>
       </c>
-      <c r="AT149" t="n">
+      <c r="AT151" t="n">
         <v>1</v>
       </c>
-      <c r="AU149" t="inlineStr">
+      <c r="AU151" t="inlineStr">
         <is>
           <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
-      <c r="AV149" t="inlineStr">
+      <c r="AV151" t="inlineStr">
         <is>
           <t>cdc_weekly</t>
         </is>
       </c>
-      <c r="AW149" t="inlineStr">
+      <c r="AW151" t="inlineStr">
         <is>
           <t>China CDC Weekly</t>
         </is>
       </c>
-      <c r="AX149" t="inlineStr">
+      <c r="AX151" t="inlineStr">
         <is>
           <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
-      <c r="AY149" t="inlineStr">
+      <c r="AY151" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ149" t="inlineStr">
+      <c r="AZ151" t="inlineStr">
         <is>
           <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
-      <c r="BA149" t="inlineStr">
+      <c r="BA151" t="inlineStr">
         <is>
           <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
-      <c r="BB149" t="inlineStr">
+      <c r="BB151" t="inlineStr">
         <is>
           <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
-      <c r="BC149" t="inlineStr">
+      <c r="BC151" t="inlineStr">
         <is>
           <t>web; web; web</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>D026</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>typhoid-and-paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Typhoid and Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>CN-CQ</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Chongqing, China</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>D026</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Typhoid and Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>伤寒和副伤寒</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N152" t="n">
+        <v>8</v>
+      </c>
+      <c r="O152" t="n">
+        <v>8</v>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO152" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP152" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ152" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS152" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_TYPHOID_PARATYPHOID; SER_CN_PROV_REPORT_TYPHOID_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="AT152" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU152" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV152" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX152" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA152" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB152" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
+        </is>
+      </c>
+      <c r="BC152" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>D026</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>typhoid-and-paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Typhoid and Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>CN-CQ</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Chongqing, China</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>D026</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Typhoid and Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>伤寒和副伤寒</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N153" t="n">
+        <v>8</v>
+      </c>
+      <c r="O153" t="n">
+        <v>8</v>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_TYPHOID_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_TYPHOID_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X153" t="inlineStr">
+        <is>
+          <t>伤寒和副伤寒</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>country:CN-CQ:national</t>
+        </is>
+      </c>
+      <c r="AD153" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE153" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF153" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG153" t="inlineStr">
+        <is>
+          <t>reported_aggregate</t>
+        </is>
+      </c>
+      <c r="AH153" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI153" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ153" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK153" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM153" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN153" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO153" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP153" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ153" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS153" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_TYPHOID_PARATYPHOID; SER_CN_PROV_REPORT_TYPHOID_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="AT153" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU153" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV153" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA153" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB153" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
+        </is>
+      </c>
+      <c r="BC153" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>D026</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>typhoid-and-paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Typhoid and Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>CN-GD</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Guangdong, China</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>D026</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Typhoid and Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>伤寒和副伤寒</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N154" t="n">
+        <v>68</v>
+      </c>
+      <c r="O154" t="n">
+        <v>68</v>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO154" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP154" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ154" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS154" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_TYPHOID_PARATYPHOID; SER_CN_PROV_REPORT_TYPHOID_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="AT154" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU154" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV154" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW154" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX154" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY154" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA154" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB154" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+        </is>
+      </c>
+      <c r="BC154" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>D026</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>typhoid-and-paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Typhoid and Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>CN-GD</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Guangdong, China</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>D026</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Typhoid and Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>伤寒和副伤寒</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N155" t="n">
+        <v>68</v>
+      </c>
+      <c r="O155" t="n">
+        <v>68</v>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_TYPHOID_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_TYPHOID_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X155" t="inlineStr">
+        <is>
+          <t>伤寒和副伤寒</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>country:CN-GD:national</t>
+        </is>
+      </c>
+      <c r="AD155" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE155" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF155" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG155" t="inlineStr">
+        <is>
+          <t>reported_aggregate</t>
+        </is>
+      </c>
+      <c r="AH155" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI155" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ155" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK155" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM155" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN155" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO155" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP155" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ155" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS155" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_TYPHOID_PARATYPHOID; SER_CN_PROV_REPORT_TYPHOID_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="AT155" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU155" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV155" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA155" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB155" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+        </is>
+      </c>
+      <c r="BC155" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>D026</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>typhoid-and-paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Typhoid and Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>CN-HN</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Hunan, China</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>D026</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Typhoid and Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>伤寒和副伤寒</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N156" t="n">
+        <v>41</v>
+      </c>
+      <c r="O156" t="n">
+        <v>41</v>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO156" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP156" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ156" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS156" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_TYPHOID_PARATYPHOID; SER_CN_PROV_REPORT_TYPHOID_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="AT156" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU156" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV156" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW156" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX156" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA156" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB156" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+        </is>
+      </c>
+      <c r="BC156" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>D026</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>typhoid-and-paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Typhoid and Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>CN-HN</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Hunan, China</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>D026</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Typhoid and Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>伤寒和副伤寒</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N157" t="n">
+        <v>41</v>
+      </c>
+      <c r="O157" t="n">
+        <v>41</v>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_TYPHOID_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_TYPHOID_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X157" t="inlineStr">
+        <is>
+          <t>伤寒和副伤寒</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>country:CN-HN:national</t>
+        </is>
+      </c>
+      <c r="AD157" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE157" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF157" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG157" t="inlineStr">
+        <is>
+          <t>reported_aggregate</t>
+        </is>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM157" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN157" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO157" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP157" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ157" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS157" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_TYPHOID_PARATYPHOID; SER_CN_PROV_REPORT_TYPHOID_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="AT157" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU157" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV157" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX157" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA157" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB157" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+        </is>
+      </c>
+      <c r="BC157" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>D026</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>typhoid-and-paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Typhoid and Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>CN-JS</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Jiangsu, China</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>D026</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Typhoid and Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>伤寒和副伤寒</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N158" t="n">
+        <v>5</v>
+      </c>
+      <c r="O158" t="n">
+        <v>5</v>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO158" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP158" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ158" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS158" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_TYPHOID_PARATYPHOID; SER_CN_PROV_REPORT_TYPHOID_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="AT158" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU158" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV158" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX158" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA158" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB158" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+        </is>
+      </c>
+      <c r="BC158" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>D026</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>typhoid-and-paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Typhoid and Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>CN-JS</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Jiangsu, China</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>D026</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Typhoid and Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>伤寒和副伤寒</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N159" t="n">
+        <v>5</v>
+      </c>
+      <c r="O159" t="n">
+        <v>5</v>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_TYPHOID_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_TYPHOID_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X159" t="inlineStr">
+        <is>
+          <t>伤寒和副伤寒</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>country:CN-JS:national</t>
+        </is>
+      </c>
+      <c r="AD159" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE159" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF159" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG159" t="inlineStr">
+        <is>
+          <t>reported_aggregate</t>
+        </is>
+      </c>
+      <c r="AH159" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI159" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ159" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK159" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM159" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN159" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO159" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP159" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ159" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS159" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_TYPHOID_PARATYPHOID; SER_CN_PROV_REPORT_TYPHOID_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="AT159" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU159" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV159" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX159" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA159" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB159" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+        </is>
+      </c>
+      <c r="BC159" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>D026</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>typhoid-and-paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Typhoid and Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>CN-LN</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Liaoning, China</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>D026</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Typhoid and Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>伤寒和副伤寒</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N160" t="n">
+        <v>8</v>
+      </c>
+      <c r="O160" t="n">
+        <v>8</v>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO160" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP160" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ160" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS160" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_TYPHOID_PARATYPHOID; SER_CN_PROV_REPORT_TYPHOID_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="AT160" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU160" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV160" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW160" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX160" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY160" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA160" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB160" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+        </is>
+      </c>
+      <c r="BC160" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>D026</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>typhoid-and-paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Typhoid and Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>CN-LN</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Liaoning, China</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>D026</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Typhoid and Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>伤寒和副伤寒</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N161" t="n">
+        <v>8</v>
+      </c>
+      <c r="O161" t="n">
+        <v>8</v>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_TYPHOID_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_TYPHOID_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X161" t="inlineStr">
+        <is>
+          <t>伤寒和副伤寒</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB161" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>country:CN-LN:national</t>
+        </is>
+      </c>
+      <c r="AD161" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE161" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF161" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG161" t="inlineStr">
+        <is>
+          <t>reported_aggregate</t>
+        </is>
+      </c>
+      <c r="AH161" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI161" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ161" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK161" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM161" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN161" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO161" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP161" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ161" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS161" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_TYPHOID_PARATYPHOID; SER_CN_PROV_REPORT_TYPHOID_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="AT161" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU161" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV161" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW161" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX161" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY161" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA161" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB161" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+        </is>
+      </c>
+      <c r="BC161" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>D026</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>typhoid-and-paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Typhoid and Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>CN-SC</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Sichuan, China</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>D026</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Typhoid and Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>伤寒和副伤寒</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N162" t="n">
+        <v>46</v>
+      </c>
+      <c r="O162" t="n">
+        <v>46</v>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO162" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP162" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ162" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS162" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_TYPHOID_PARATYPHOID; SER_CN_PROV_REPORT_TYPHOID_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="AT162" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU162" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV162" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW162" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX162" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY162" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA162" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB162" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+        </is>
+      </c>
+      <c r="BC162" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>D026</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>typhoid-and-paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Typhoid and Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>CN-SC</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Sichuan, China</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>D026</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Typhoid and Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>伤寒和副伤寒</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N163" t="n">
+        <v>46</v>
+      </c>
+      <c r="O163" t="n">
+        <v>46</v>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_TYPHOID_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_TYPHOID_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X163" t="inlineStr">
+        <is>
+          <t>伤寒和副伤寒</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB163" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>country:CN-SC:national</t>
+        </is>
+      </c>
+      <c r="AD163" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE163" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF163" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG163" t="inlineStr">
+        <is>
+          <t>reported_aggregate</t>
+        </is>
+      </c>
+      <c r="AH163" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI163" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ163" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK163" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM163" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN163" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO163" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP163" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ163" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_TYPHOID_PARATYPHOID; SER_CN_PROV_REPORT_TYPHOID_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="AT163" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU163" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV163" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW163" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX163" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA163" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB163" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+        </is>
+      </c>
+      <c r="BC163" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>D026</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>typhoid-and-paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Typhoid and Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>CN-SH</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Shanghai, China</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>D026</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Typhoid and Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>伤寒和副伤寒</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N164" t="n">
+        <v>1</v>
+      </c>
+      <c r="O164" t="n">
+        <v>1</v>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO164" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP164" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ164" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS164" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_TYPHOID_PARATYPHOID; SER_CN_PROV_REPORT_TYPHOID_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="AT164" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU164" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV164" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW164" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX164" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA164" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB164" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+        </is>
+      </c>
+      <c r="BC164" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>D026</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>typhoid-and-paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Typhoid and Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>CN-SH</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Shanghai, China</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>D026</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Typhoid and Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>伤寒和副伤寒</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N165" t="n">
+        <v>1</v>
+      </c>
+      <c r="O165" t="n">
+        <v>1</v>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_TYPHOID_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_TYPHOID_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X165" t="inlineStr">
+        <is>
+          <t>伤寒和副伤寒</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>country:CN-SH:national</t>
+        </is>
+      </c>
+      <c r="AD165" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE165" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF165" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG165" t="inlineStr">
+        <is>
+          <t>reported_aggregate</t>
+        </is>
+      </c>
+      <c r="AH165" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI165" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ165" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK165" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM165" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN165" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO165" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP165" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ165" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS165" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_TYPHOID_PARATYPHOID; SER_CN_PROV_REPORT_TYPHOID_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="AT165" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU165" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV165" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW165" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX165" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY165" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA165" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB165" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+        </is>
+      </c>
+      <c r="BC165" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -28224,7 +31304,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>87</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10">
@@ -28234,7 +31314,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>148</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11">
@@ -28254,7 +31334,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13">
@@ -28286,7 +31366,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3645</v>
+        <v>3847</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d026/2026-2029.xlsx
+++ b/diseases/d026/2026-2029.xlsx
@@ -11272,6 +11272,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11420,6 +11425,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11568,6 +11578,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14958,6 +14973,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15106,6 +15126,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15254,6 +15279,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15402,6 +15432,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19177,6 +19212,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19325,6 +19365,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19473,6 +19518,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19621,6 +19671,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19769,6 +19824,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23156,6 +23216,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23301,6 +23366,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23446,6 +23516,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23591,6 +23666,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27597,6 +27677,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO146" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27742,6 +27827,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27887,6 +27977,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28030,6 +28125,11 @@
       <c r="S149" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO149" t="inlineStr">

--- a/diseases/d026/2026-2029.xlsx
+++ b/diseases/d026/2026-2029.xlsx
@@ -5295,17 +5295,15 @@
       <c r="O34" t="n">
         <v>1</v>
       </c>
+      <c r="P34" t="n">
+        <v>1</v>
+      </c>
       <c r="Q34" t="n">
         <v>0</v>
       </c>
       <c r="R34" t="n">
         <v>0.0002865038132769385</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5318,23 +5316,13 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
       </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV34" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -5448,17 +5436,15 @@
       <c r="O35" t="n">
         <v>1</v>
       </c>
+      <c r="P35" t="n">
+        <v>1</v>
+      </c>
       <c r="Q35" t="n">
         <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0.0002865038132769385</v>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5471,23 +5457,13 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
       </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV35" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -5601,17 +5577,15 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
       <c r="Q36" t="n">
         <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5624,23 +5598,13 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
       </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV36" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -7170,17 +7134,15 @@
       <c r="O47" t="n">
         <v>1</v>
       </c>
+      <c r="P47" t="n">
+        <v>1</v>
+      </c>
       <c r="Q47" t="n">
         <v>0</v>
       </c>
       <c r="R47" t="n">
         <v>0.0002865038132769385</v>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7193,23 +7155,13 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
       </c>
-      <c r="AU47" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV47" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -7323,17 +7275,15 @@
       <c r="O48" t="n">
         <v>1</v>
       </c>
+      <c r="P48" t="n">
+        <v>1</v>
+      </c>
       <c r="Q48" t="n">
         <v>0</v>
       </c>
       <c r="R48" t="n">
         <v>0.0002865038132769385</v>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7346,23 +7296,13 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR48" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
       </c>
-      <c r="AU48" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV48" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -7476,17 +7416,15 @@
       <c r="O49" t="n">
         <v>1</v>
       </c>
+      <c r="P49" t="n">
+        <v>1</v>
+      </c>
       <c r="Q49" t="n">
         <v>0</v>
       </c>
       <c r="R49" t="n">
         <v>0.0002865038132769385</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7499,23 +7437,13 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
       </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV49" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -7629,17 +7557,15 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
       <c r="Q50" t="n">
         <v>0</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7652,23 +7578,13 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
       </c>
-      <c r="AU50" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV50" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -9621,17 +9537,15 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
+      <c r="P64" t="n">
+        <v>0</v>
+      </c>
       <c r="Q64" t="n">
         <v>0</v>
       </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -9644,23 +9558,13 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR64" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="n">
         <v>0</v>
       </c>
-      <c r="AU64" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV64" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -9774,17 +9678,15 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
       <c r="Q65" t="n">
         <v>0</v>
       </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -9797,23 +9699,13 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR65" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="n">
         <v>0</v>
       </c>
-      <c r="AU65" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV65" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -9927,17 +9819,15 @@
       <c r="O66" t="n">
         <v>1</v>
       </c>
+      <c r="P66" t="n">
+        <v>1</v>
+      </c>
       <c r="Q66" t="n">
         <v>0</v>
       </c>
       <c r="R66" t="n">
         <v>0.0002865038132769385</v>
       </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -9950,23 +9840,13 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR66" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="n">
         <v>0</v>
       </c>
-      <c r="AU66" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV66" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -10080,17 +9960,15 @@
       <c r="O67" t="n">
         <v>1</v>
       </c>
+      <c r="P67" t="n">
+        <v>1</v>
+      </c>
       <c r="Q67" t="n">
         <v>0</v>
       </c>
       <c r="R67" t="n">
         <v>0.0002865038132769385</v>
       </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -10103,23 +9981,13 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR67" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="n">
         <v>0</v>
       </c>
-      <c r="AU67" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV67" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -10233,17 +10101,15 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
+      <c r="P68" t="n">
+        <v>0</v>
+      </c>
       <c r="Q68" t="n">
         <v>0</v>
       </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -10256,23 +10122,13 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR68" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="n">
         <v>0</v>
       </c>
-      <c r="AU68" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV68" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -12225,14 +12081,12 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -12245,23 +12099,13 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR82" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="n">
         <v>0</v>
       </c>
-      <c r="AU82" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV82" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -12375,14 +12219,12 @@
       <c r="O83" t="n">
         <v>1</v>
       </c>
+      <c r="P83" t="n">
+        <v>1</v>
+      </c>
       <c r="R83" t="n">
         <v>0.0002865038132769385</v>
       </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -12395,23 +12237,13 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR83" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="n">
         <v>0</v>
       </c>
-      <c r="AU83" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV83" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -12525,14 +12357,12 @@
       <c r="O84" t="n">
         <v>1</v>
       </c>
+      <c r="P84" t="n">
+        <v>1</v>
+      </c>
       <c r="R84" t="n">
         <v>0.0002865038132769385</v>
       </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -12545,23 +12375,13 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR84" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="n">
         <v>0</v>
       </c>
-      <c r="AU84" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV84" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -12675,14 +12495,12 @@
       <c r="O85" t="n">
         <v>1</v>
       </c>
+      <c r="P85" t="n">
+        <v>1</v>
+      </c>
       <c r="R85" t="n">
         <v>0.0002865038132769385</v>
       </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -12695,23 +12513,13 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR85" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="n">
         <v>0</v>
       </c>
-      <c r="AU85" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV85" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -14664,14 +14472,12 @@
       <c r="O99" t="n">
         <v>0</v>
       </c>
+      <c r="P99" t="n">
+        <v>0</v>
+      </c>
       <c r="R99" t="n">
         <v>0</v>
       </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -14684,23 +14490,13 @@
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR99" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="n">
         <v>0</v>
       </c>
-      <c r="AU99" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV99" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -14814,14 +14610,12 @@
       <c r="O100" t="n">
         <v>0</v>
       </c>
+      <c r="P100" t="n">
+        <v>0</v>
+      </c>
       <c r="R100" t="n">
         <v>0</v>
       </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -14834,23 +14628,13 @@
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR100" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="n">
         <v>0</v>
       </c>
-      <c r="AU100" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV100" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -14964,14 +14748,12 @@
       <c r="O101" t="n">
         <v>2</v>
       </c>
+      <c r="P101" t="n">
+        <v>2</v>
+      </c>
       <c r="R101" t="n">
         <v>0.0005730076265538771</v>
       </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -14984,23 +14766,13 @@
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR101" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="n">
         <v>0</v>
       </c>
-      <c r="AU101" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV101" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -15114,14 +14886,12 @@
       <c r="O102" t="n">
         <v>0</v>
       </c>
+      <c r="P102" t="n">
+        <v>0</v>
+      </c>
       <c r="R102" t="n">
         <v>0</v>
       </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -15134,22 +14904,12 @@
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR102" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr"/>
       <c r="AT102" t="n">
         <v>0</v>
-      </c>
-      <c r="AU102" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
